--- a/multiSchoolOutput/02_School_of_Mathematics/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/02_School_of_Mathematics/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0110_02_2.04</t>
+          <t>0210_00_GFS1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0003_00_G.04</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9945,12 +9945,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10006,12 +10006,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10311,12 +10311,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11653,12 +11653,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12812,12 +12812,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0113_00_G.152</t>
+          <t>0226_00_GF.Z16</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13117,12 +13117,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13483,12 +13483,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14093,12 +14093,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -14154,12 +14154,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14398,12 +14398,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14581,12 +14581,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14703,12 +14703,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14764,12 +14764,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14886,12 +14886,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -15130,12 +15130,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -15252,12 +15252,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -15313,12 +15313,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15496,12 +15496,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15679,12 +15679,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15801,12 +15801,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15862,12 +15862,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15923,12 +15923,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -16045,12 +16045,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -16106,12 +16106,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>0001_02_2.351</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16289,12 +16289,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16350,12 +16350,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16411,12 +16411,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>0228_03_3.01</t>
+          <t>0001_01_1.266</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16533,12 +16533,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16594,12 +16594,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16655,12 +16655,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16777,12 +16777,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16838,12 +16838,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16899,12 +16899,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -17204,12 +17204,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -17326,12 +17326,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17448,12 +17448,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17570,12 +17570,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17631,12 +17631,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17692,12 +17692,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17753,12 +17753,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -17814,12 +17814,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17875,12 +17875,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17941,7 +17941,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -18119,12 +18119,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0003_00_G.04</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -18241,12 +18241,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -18302,12 +18302,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18363,12 +18363,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18485,12 +18485,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18546,12 +18546,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18607,12 +18607,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18668,12 +18668,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -18729,12 +18729,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -18790,12 +18790,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -18912,12 +18912,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -18973,12 +18973,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -19034,12 +19034,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19156,12 +19156,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -19339,12 +19339,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19400,12 +19400,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -19461,12 +19461,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -19522,12 +19522,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>0113_00_G.152</t>
+          <t>0226_00_GF.Z16</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -19644,12 +19644,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -19766,12 +19766,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19888,12 +19888,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20010,12 +20010,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -20071,12 +20071,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -20132,12 +20132,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -20254,12 +20254,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -20437,12 +20437,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -20559,12 +20559,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -20620,12 +20620,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -20681,12 +20681,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -20742,12 +20742,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0228_03_3.01</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20864,12 +20864,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -20986,12 +20986,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -21047,12 +21047,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -21230,12 +21230,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -21291,12 +21291,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -21352,12 +21352,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -21413,12 +21413,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>0228_-1_LG.09</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -21474,12 +21474,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -21535,12 +21535,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -21596,12 +21596,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -21718,12 +21718,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -21779,12 +21779,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -21840,12 +21840,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -21901,12 +21901,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -21962,12 +21962,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -22023,12 +22023,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -22084,12 +22084,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22206,12 +22206,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -22328,12 +22328,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -22389,12 +22389,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -22450,12 +22450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -22572,12 +22572,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -22694,12 +22694,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -22755,12 +22755,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -22816,12 +22816,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -22877,12 +22877,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -22999,12 +22999,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -23060,12 +23060,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -23121,12 +23121,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -23182,12 +23182,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -23304,12 +23304,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -23426,12 +23426,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>0003_01_1.02</t>
+          <t>0001_01_1.266</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -23487,12 +23487,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -23548,12 +23548,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -23609,12 +23609,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -23670,12 +23670,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -23731,12 +23731,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -23792,12 +23792,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -23853,12 +23853,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -23975,12 +23975,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -24158,12 +24158,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -24219,12 +24219,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24402,12 +24402,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0228_07_7.18</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -24463,12 +24463,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -24524,12 +24524,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -24646,12 +24646,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -24707,12 +24707,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -24768,12 +24768,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -24829,12 +24829,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -24951,12 +24951,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -25012,12 +25012,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -25073,12 +25073,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -25134,12 +25134,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -25195,12 +25195,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -25256,12 +25256,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -25317,12 +25317,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -25378,12 +25378,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -25439,12 +25439,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -25500,12 +25500,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -25561,12 +25561,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25683,12 +25683,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -25744,12 +25744,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -25805,12 +25805,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -25988,12 +25988,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -26049,12 +26049,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -26110,12 +26110,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>0228_09_9.01</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -26232,12 +26232,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -26293,12 +26293,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -26354,12 +26354,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -26415,12 +26415,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -26481,7 +26481,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -26537,12 +26537,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26603,7 +26603,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -26659,12 +26659,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26720,12 +26720,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -26781,12 +26781,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -26842,12 +26842,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -26903,12 +26903,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -27025,12 +27025,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -27086,12 +27086,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -27147,12 +27147,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -27208,12 +27208,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27330,12 +27330,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -27391,12 +27391,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>0226_00_GF.Z16</t>
+          <t>0113_00_G.152</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -27452,12 +27452,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -27513,12 +27513,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -27579,7 +27579,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27635,12 +27635,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -27696,12 +27696,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -27757,12 +27757,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -27818,12 +27818,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -27879,12 +27879,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -27940,12 +27940,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -28001,12 +28001,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -28067,7 +28067,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -28123,12 +28123,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -28184,12 +28184,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -28245,7 +28245,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28306,12 +28306,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -28367,12 +28367,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -28428,12 +28428,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -28550,12 +28550,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -28611,12 +28611,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -28672,12 +28672,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -28794,12 +28794,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -28855,12 +28855,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -28916,12 +28916,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -28977,12 +28977,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -29038,12 +29038,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -29099,12 +29099,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -29282,12 +29282,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29343,12 +29343,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -29404,12 +29404,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -29465,12 +29465,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -29526,12 +29526,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29587,12 +29587,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -29648,12 +29648,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -29770,12 +29770,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -29831,12 +29831,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -29892,12 +29892,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -29953,12 +29953,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -30014,7 +30014,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>0300_00_NG.04</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30075,12 +30075,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>0228_-1_LG.09</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -30136,12 +30136,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -30197,12 +30197,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -30319,12 +30319,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -30385,7 +30385,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -30441,12 +30441,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0003_00_G.04</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -30563,12 +30563,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -30624,12 +30624,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -30685,12 +30685,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -30746,12 +30746,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -30807,12 +30807,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -30873,7 +30873,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -30990,12 +30990,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -31112,12 +31112,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -31234,12 +31234,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -31300,7 +31300,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -31356,12 +31356,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -31417,12 +31417,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -31478,12 +31478,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -31539,12 +31539,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -31600,12 +31600,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -31661,12 +31661,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -31783,12 +31783,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -31844,12 +31844,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -31905,7 +31905,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -31966,12 +31966,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -32027,12 +32027,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -32088,12 +32088,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -32154,7 +32154,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -32210,12 +32210,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -32271,12 +32271,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -32332,12 +32332,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -32393,12 +32393,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -32454,12 +32454,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0113_02_2.27</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -32515,12 +32515,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -32576,12 +32576,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -32637,12 +32637,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -32698,12 +32698,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32820,12 +32820,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -32886,7 +32886,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -33003,12 +33003,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -33064,12 +33064,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -33130,7 +33130,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -33186,12 +33186,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -33252,7 +33252,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -33308,12 +33308,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -33369,12 +33369,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0003_00_G.04</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -33430,12 +33430,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -33491,12 +33491,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -33552,12 +33552,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -33613,12 +33613,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -33674,12 +33674,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -33735,12 +33735,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -33796,7 +33796,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33857,12 +33857,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -33923,7 +33923,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -33979,12 +33979,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -34040,12 +34040,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -34101,7 +34101,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34162,12 +34162,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -34223,12 +34223,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -34284,12 +34284,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -34345,12 +34345,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -34467,12 +34467,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -34528,7 +34528,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -34589,12 +34589,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -34711,12 +34711,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -34772,12 +34772,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -34833,7 +34833,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -34894,12 +34894,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -34955,12 +34955,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -35016,12 +35016,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -35077,7 +35077,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -35138,12 +35138,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>0335_01_1.4</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -35199,12 +35199,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -35260,12 +35260,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -35321,12 +35321,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -35382,12 +35382,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
